--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92563</v>
+        <v>92566</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92566</v>
+        <v>92567</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -2167,7 +2167,7 @@
         <v>136252206</v>
       </c>
       <c r="B16" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>136252251</v>
       </c>
       <c r="B17" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>136252510</v>
       </c>
       <c r="B18" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136252492</v>
       </c>
       <c r="B21" t="n">
-        <v>83452</v>
+        <v>83454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>136252584</v>
       </c>
       <c r="B23" t="n">
-        <v>79543</v>
+        <v>79545</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136252259</v>
       </c>
       <c r="B37" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>136252411</v>
       </c>
       <c r="B38" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>136252520</v>
       </c>
       <c r="B39" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>136252894</v>
       </c>
       <c r="B40" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>136252214</v>
       </c>
       <c r="B73" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>136252239</v>
       </c>
       <c r="B74" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>136252374</v>
       </c>
       <c r="B75" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>136252691</v>
       </c>
       <c r="B76" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>136252717</v>
       </c>
       <c r="B77" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>136252731</v>
       </c>
       <c r="B78" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>136252743</v>
       </c>
       <c r="B79" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136252776</v>
       </c>
       <c r="B80" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>136252794</v>
       </c>
       <c r="B81" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>136252848</v>
       </c>
       <c r="B82" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>136252877</v>
       </c>
       <c r="B83" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>136252954</v>
       </c>
       <c r="B84" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92567</v>
+        <v>92572</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>136252457</v>
       </c>
       <c r="B110" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136252545</v>
       </c>
       <c r="B111" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>136252698</v>
       </c>
       <c r="B112" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>136252712</v>
       </c>
       <c r="B113" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>136252748</v>
       </c>
       <c r="B114" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>136252797</v>
       </c>
       <c r="B115" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>136252368</v>
       </c>
       <c r="B121" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>136252235</v>
       </c>
       <c r="B127" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>136252481</v>
       </c>
       <c r="B130" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>136252863</v>
       </c>
       <c r="B134" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>136252672</v>
       </c>
       <c r="B139" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>136252454</v>
       </c>
       <c r="B146" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>136252833</v>
       </c>
       <c r="B150" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>

--- a/artfynd/A 25045-2024 artfynd.xlsx
+++ b/artfynd/A 25045-2024 artfynd.xlsx
@@ -5246,7 +5246,7 @@
         <v>136252466</v>
       </c>
       <c r="B45" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>136252770</v>
       </c>
       <c r="B46" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>136252908</v>
       </c>
       <c r="B47" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>136252218</v>
       </c>
       <c r="B86" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136252271</v>
       </c>
       <c r="B93" t="n">
-        <v>92572</v>
+        <v>92574</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>136252222</v>
       </c>
       <c r="B166" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>136252915</v>
       </c>
       <c r="B167" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
